--- a/AAII_Financials/Quarterly/OPI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OPI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>OPI</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -688,448 +688,499 @@
     <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>108900</v>
+      </c>
+      <c r="F8" s="3">
+        <v>105300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>109100</v>
+      </c>
+      <c r="H8" s="3">
         <v>114500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="I8" s="3">
         <v>113600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="J8" s="3">
         <v>118200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="K8" s="3">
         <v>120600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>123700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>139400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>133800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>133400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>134000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>132400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>127900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>137700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>141300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>147400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>147300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>147600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>137100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>144500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>146600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>145800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>145600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>149900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>160200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>167400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>176000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>174800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>103700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>106100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>216800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AK8" s="3">
         <v>108700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AL8" s="3">
         <v>107200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AM8" s="3">
         <v>70200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AN8" s="3">
         <v>139200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AO8" s="3">
         <v>69300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15700</v>
+      </c>
+      <c r="G9" s="3">
+        <v>21400</v>
+      </c>
+      <c r="H9" s="3">
         <v>17800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="I9" s="3">
         <v>21000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="J9" s="3">
         <v>20700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="K9" s="3">
         <v>24800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>20500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>23900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>23700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>21700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>21600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>22600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>37000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>44200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>43100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>44000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>48800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>46600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>40800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>41600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>43900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>42500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>41600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>42700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>49100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AE9" s="3">
         <v>49200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>47800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>48500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>35700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>33900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>69800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AK9" s="3">
         <v>35800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AL9" s="3">
         <v>34300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AM9" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AN9" s="3">
         <v>45300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AO9" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>86700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>89600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>87800</v>
+      </c>
+      <c r="H10" s="3">
         <v>96700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="I10" s="3">
         <v>92600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="J10" s="3">
         <v>97500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="K10" s="3">
         <v>95800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>103200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>115600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>110100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>111600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>112400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>109800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>90900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>93500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>98200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>103400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>98500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>101000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>96300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>102900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>102800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>103300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>104000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>107200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>111100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>118200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>128200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>126300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>68000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>72200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>147000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AK10" s="3">
         <v>72900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AL10" s="3">
         <v>72900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AM10" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AN10" s="3">
         <v>93900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AO10" s="3">
         <v>47100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1218,12 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1329,20 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,222 +1448,258 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>746200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>59500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>87200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>23300</v>
+      </c>
+      <c r="H14" s="3">
         <v>6100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="I14" s="3">
         <v>5900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="J14" s="3">
         <v>121000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="K14" s="3">
         <v>33900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="L14" s="3">
         <v>-94000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="N14" s="3">
         <v>9300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="O14" s="3">
         <v>15900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="P14" s="3">
         <v>13500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="R14" s="3">
         <v>-800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>4900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>17000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>6600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <v>2300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>60000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>7700</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>3000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>3300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AD14" s="3">
         <v>8200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AE14" s="3">
         <v>8800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AF14" s="3">
         <v>2500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AG14" s="3">
         <v>3600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AH14" s="3">
         <v>3500</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>5800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AK14" s="3">
         <v>6100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AL14" s="3">
         <v>9300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AM14" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>44100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>44600</v>
+      </c>
+      <c r="G15" s="3">
+        <v>42800</v>
+      </c>
+      <c r="H15" s="3">
         <v>43800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="I15" s="3">
         <v>43700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="J15" s="3">
         <v>48000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="K15" s="3">
         <v>46000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="L15" s="3">
         <v>50400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="M15" s="3">
         <v>50300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="N15" s="3">
         <v>53700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="O15" s="3">
         <v>52300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="P15" s="3">
         <v>51600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="Q15" s="3">
         <v>51700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="R15" s="3">
         <v>51600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="S15" s="3">
         <v>53000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="T15" s="3">
         <v>57500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="U15" s="3">
         <v>60500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <v>62500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
         <v>59500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="X15" s="3">
         <v>55400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="Y15" s="3">
         <v>64100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>62200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="AA15" s="3">
         <v>62200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AB15" s="3">
         <v>64200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AC15" s="3">
         <v>62900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AD15" s="3">
         <v>63500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AE15" s="3">
         <v>74900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AF15" s="3">
         <v>73900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AG15" s="3">
         <v>77500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AH15" s="3">
         <v>33000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AI15" s="3">
         <v>42600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AJ15" s="3">
         <v>86900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AK15" s="3">
         <v>44200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AL15" s="3">
         <v>47600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AM15" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AN15" s="3">
         <v>41200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AO15" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1734,250 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>100800</v>
+      </c>
+      <c r="F17" s="3">
+        <v>93100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>99900</v>
+      </c>
+      <c r="H17" s="3">
         <v>97700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="I17" s="3">
         <v>101000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="J17" s="3">
         <v>100200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="K17" s="3">
         <v>102400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>103300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>107200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>111900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>107600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>105700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>106300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>100000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>111700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>118600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>134100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>126100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>116200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>174500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>131000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>119000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>122300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>118700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>123000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>136000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>150500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>140500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>148400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>77400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>110400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>189200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AK17" s="3">
         <v>102400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AL17" s="3">
         <v>104500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AM17" s="3">
         <v>55100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AN17" s="3">
         <v>104300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AO17" s="3">
         <v>51200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H18" s="3">
         <v>16800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="I18" s="3">
         <v>12600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="J18" s="3">
         <v>18000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="K18" s="3">
         <v>18200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>20400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>32300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>21900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>25700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>28300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>26200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>27900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>26000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>22700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>13300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>21200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>31400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>-37400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>13500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>27600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>23500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>26900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>26900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <v>24200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <v>16900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>35500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>26400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>26300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>27600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AK18" s="3">
         <v>6300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AL18" s="3">
         <v>2700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AM18" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AN18" s="3">
         <v>34900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AO18" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,67 +2015,71 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="N20" s="3">
         <v>19900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="S20" s="3">
         <v>17000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="T20" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="V20" s="3">
         <v>24200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>54000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1953,384 +2088,432 @@
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>54000</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>11400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AD20" s="3">
         <v>71800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AE20" s="3">
         <v>11800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AF20" s="3">
         <v>-64900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AG20" s="3">
         <v>45400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AH20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AI20" s="3">
         <v>17900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AJ20" s="3">
         <v>24100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AK20" s="3">
         <v>13400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AL20" s="3">
         <v>22200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AM20" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AN20" s="3">
         <v>14700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AO20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>64500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>56800</v>
+      </c>
+      <c r="G21" s="3">
+        <v>51900</v>
+      </c>
+      <c r="H21" s="3">
         <v>60500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="I21" s="3">
         <v>56100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="J21" s="3">
         <v>65800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="K21" s="3">
         <v>64100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>70600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>82400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>55600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>77200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>79200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>77000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="R21" s="3">
         <v>81700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>94500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>67200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>74500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>106500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>89700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>17200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>130700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>89800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>85500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AB21" s="3">
         <v>91100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AC21" s="3">
         <v>101300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AD21" s="3">
         <v>158200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AE21" s="3">
         <v>102400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AF21" s="3">
         <v>44700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AG21" s="3">
         <v>149300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>31900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AI21" s="3">
         <v>55800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AJ21" s="3">
         <v>138000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AK21" s="3">
         <v>63600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AL21" s="3">
         <v>72400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AM21" s="3">
         <v>53600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AN21" s="3">
         <v>90200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AO21" s="3">
         <v>38700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F22" s="3">
+        <v>44300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>53300</v>
+      </c>
+      <c r="H22" s="3">
         <v>52500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="I22" s="3">
         <v>53400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="J22" s="3">
         <v>47300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="K22" s="3">
         <v>42600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="L22" s="3">
         <v>38300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="M22" s="3">
         <v>35500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="N22" s="3">
         <v>30100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="O22" s="3">
         <v>28800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>26500</v>
-      </c>
-      <c r="M22" s="3">
-        <v>25200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>24600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>25000</v>
       </c>
       <c r="P22" s="3">
         <v>26500</v>
       </c>
       <c r="Q22" s="3">
+        <v>25200</v>
+      </c>
+      <c r="R22" s="3">
+        <v>24600</v>
+      </c>
+      <c r="S22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="T22" s="3">
+        <v>26500</v>
+      </c>
+      <c r="U22" s="3">
         <v>27400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="V22" s="3">
         <v>27700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>26900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>29000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>28800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>28800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>27100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AB22" s="3">
         <v>25200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AC22" s="3">
         <v>27200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AD22" s="3">
         <v>30000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AE22" s="3">
         <v>32400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AF22" s="3">
         <v>35300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AG22" s="3">
         <v>37100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AH22" s="3">
         <v>20400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AI22" s="3">
         <v>23400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AJ22" s="3">
         <v>46100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AK22" s="3">
         <v>22800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AL22" s="3">
         <v>43600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AM22" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AN22" s="3">
         <v>41500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AO22" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-791900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-118800</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="H23" s="3">
         <v>-41100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="I23" s="3">
         <v>-45700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="J23" s="3">
         <v>-148700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="K23" s="3">
         <v>-58200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="L23" s="3">
         <v>76100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>-5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>-37100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>-19500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>-12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>-12000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>17700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>4400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>-66200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>38700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>11200</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>66000</v>
       </c>
       <c r="AA23" s="3">
         <v>-3600</v>
       </c>
       <c r="AB23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>11200</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>66000</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <v>34700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AI23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AJ23" s="3">
         <v>5700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AK23" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AL23" s="3">
         <v>-18700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AM23" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AN23" s="3">
         <v>8100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AO23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
@@ -2339,88 +2522,100 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
+        <v>100</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AG24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2721,258 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-792100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-41200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="I26" s="3">
         <v>-45900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="J26" s="3">
         <v>-148700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="K26" s="3">
         <v>-58400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>76200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>-37200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>-19600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>-12200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>7300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>17900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>-12600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>17800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>4400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>-66100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>38300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>-1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>-3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>1600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>11100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>65700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AF26" s="3">
         <v>-64600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <v>34300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>-21100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AJ26" s="3">
         <v>5500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AK26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AL26" s="3">
         <v>-18800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AM26" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AN26" s="3">
         <v>8000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AO26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-792100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="H27" s="3">
         <v>-41200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="I27" s="3">
         <v>-45900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="J27" s="3">
         <v>-148600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="K27" s="3">
         <v>-58400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>75700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>-5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>-37200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>-19600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>-12300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>17000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>-13400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>16900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>3700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>-66700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>37900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>10800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>65000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>34000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>-39500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AJ27" s="3">
         <v>21300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AK27" s="3">
         <v>6300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AL27" s="3">
         <v>-19600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AM27" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AN27" s="3">
         <v>8500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AO27" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +3078,20 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2912,50 +3155,62 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-18200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AI29" s="3">
         <v>9300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AJ29" s="3">
         <v>14600</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AM29" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AN29" s="3">
         <v>10600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AO29" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3316,20 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,67 +3435,79 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="N32" s="3">
         <v>-19900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="S32" s="3">
         <v>-17000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="T32" s="3">
         <v>11600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="V32" s="3">
         <v>-24200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-54000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -3237,153 +3516,177 @@
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AD32" s="3">
         <v>-71800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AE32" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AF32" s="3">
         <v>64900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AG32" s="3">
         <v>-45400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AH32" s="3">
         <v>27000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AI32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AJ32" s="3">
         <v>-24100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AK32" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AL32" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AM32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AN32" s="3">
         <v>-14700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AO32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-792100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="H33" s="3">
         <v>-41200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="I33" s="3">
         <v>-45900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="J33" s="3">
         <v>-148700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="K33" s="3">
         <v>-58400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>76200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>-5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>-37200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>-19600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>-12200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>17000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>-13400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>16900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>-66700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>37900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>-3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>10800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>65000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>34000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>-57700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>-400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AJ33" s="3">
         <v>35900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AK33" s="3">
         <v>6300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AL33" s="3">
         <v>-18300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AM33" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AN33" s="3">
         <v>19100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AO33" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3792,263 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-792100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="H35" s="3">
         <v>-41200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="I35" s="3">
         <v>-45900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="J35" s="3">
         <v>-148700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="K35" s="3">
         <v>-58400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>76200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>-5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>-37200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>-19600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>-12200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>17000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>-13400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>16900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>-66700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>37900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>-3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>10800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>65000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>34000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>-57700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>-400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AJ35" s="3">
         <v>35900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AK35" s="3">
         <v>6300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AL35" s="3">
         <v>-18300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AM35" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AN35" s="3">
         <v>19100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AO35" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +4086,12 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +4129,131 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>26300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>29500</v>
+      </c>
+      <c r="G41" s="3">
+        <v>44600</v>
+      </c>
+      <c r="H41" s="3">
         <v>78200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>63700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>261300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>22400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>13500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>23500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>12300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>24400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>25200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>23300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>12200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>14000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>26000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>97700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>83000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>54900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>18700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>184500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>42000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>45000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>24500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>29700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>93700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>29000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>21100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AG41" s="3">
         <v>20200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AH41" s="3">
         <v>35300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AI41" s="3">
         <v>9600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AJ41" s="3">
         <v>18700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AK41" s="3">
         <v>17400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AL41" s="3">
         <v>16600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AM41" s="3">
         <v>551700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AN41" s="3">
         <v>12900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AO41" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,115 +4359,139 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>172200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>164300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>162600</v>
+      </c>
+      <c r="H43" s="3">
         <v>163400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>150700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>155700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>146600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>140500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>137500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>133300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>124000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>110600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>107000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>105600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>105900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>103400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>106900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>112900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>97500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>91000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>94900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>101800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>100400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>95000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>90500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>83600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>70200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>70600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AG43" s="3">
         <v>67800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AH43" s="3">
         <v>72100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AI43" s="3">
         <v>55300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AJ43" s="3">
         <v>61500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AK43" s="3">
         <v>65500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AL43" s="3">
         <v>61400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AM43" s="3">
         <v>47500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AN43" s="3">
         <v>47700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AO43" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4142,17 +4525,17 @@
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4214,53 +4597,65 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>295000</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H45" s="3">
         <v>8700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>32200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>125800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>117800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>11900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>37300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>11700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4321,53 +4716,65 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>417300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>259900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>245000</v>
+      </c>
+      <c r="G46" s="3">
+        <v>227800</v>
+      </c>
+      <c r="H46" s="3">
         <v>264000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>238400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>463000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>308600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>292700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>193500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>197300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>180600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>148200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>134900</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4428,222 +4835,258 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17000</v>
+        <v>12900</v>
       </c>
       <c r="E47" s="3">
         <v>17100</v>
       </c>
       <c r="F47" s="3">
+        <v>17000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>16900</v>
+      </c>
+      <c r="H47" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J47" s="3">
         <v>17400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>17600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>17700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>17900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>18100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>36600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>37400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>36600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>35100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>35100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>35300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>35000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>34800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>35800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>36700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>37400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>38000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>38500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="AB47" s="3">
         <v>39100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AC47" s="3">
         <v>39400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AD47" s="3">
         <v>39800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AE47" s="3">
         <v>40500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AF47" s="3">
         <v>41600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AG47" s="3">
         <v>42500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AH47" s="3">
         <v>43700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AI47" s="3">
         <v>498400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AJ47" s="3">
         <v>503500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AK47" s="3">
         <v>513900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AL47" s="3">
         <v>517700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AM47" s="3">
         <v>475300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AN47" s="3">
         <v>477200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AO47" s="3">
         <v>482100</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1106500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2924100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2947200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2967700</v>
+      </c>
+      <c r="H48" s="3">
         <v>2990000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>3009700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>3038900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>3077100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>3171400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>3401000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>3415500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>3436000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>3429800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>3410100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>3743900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>3734200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>3732600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>3836200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>3920800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>3915100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>3963300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>3513300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>3619300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>3695500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AB48" s="3">
         <v>3758900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AC48" s="3">
         <v>3803800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AD48" s="3">
         <v>3838000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AE48" s="3">
         <v>3990000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AF48" s="3">
         <v>4346900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AG48" s="3">
         <v>4534600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AH48" s="3">
         <v>4626000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AI48" s="3">
         <v>2351500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AJ48" s="3">
         <v>2784900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AK48" s="3">
         <v>2907100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AL48" s="3">
         <v>2985700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AM48" s="3">
         <v>1698600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AN48" s="3">
         <v>1710900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AO48" s="3">
         <v>1719300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4749,8 +5192,20 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +5311,20 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5430,139 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>835200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>170900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>184000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>193400</v>
+      </c>
+      <c r="H52" s="3">
         <v>191300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>205500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>199900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>227200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>234600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>259700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>271700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>306700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>329600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>352600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>75600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>70000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>162400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>114000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>82000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>125200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="X52" s="3">
         <v>95300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Y52" s="3">
         <v>109600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Z52" s="3">
         <v>132600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AA52" s="3">
         <v>77800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AB52" s="3">
         <v>50600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AC52" s="3">
         <v>47000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AD52" s="3">
         <v>117900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AE52" s="3">
         <v>197300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AF52" s="3">
         <v>164300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AG52" s="3">
         <v>59300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AH52" s="3">
         <v>282800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AI52" s="3">
         <v>433200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AJ52" s="3">
         <v>25300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AK52" s="3">
         <v>45500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AL52" s="3">
         <v>26100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AM52" s="3">
         <v>22800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AN52" s="3">
         <v>34100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AO52" s="3">
         <v>34500</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5668,139 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2374500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3467900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>3488600</v>
+      </c>
+      <c r="G54" s="3">
+        <v>3501400</v>
+      </c>
+      <c r="H54" s="3">
         <v>3560900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>3569800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>3822300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>3726000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>3799900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>3957900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>3989700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>4045000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>4027600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>4007000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>3980000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>3969000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>4062700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>4197700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>4241700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>4239900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>4211200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>3952600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>3946400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>3973000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>3977700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>4028700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>4193100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>4360200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>4804300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AG54" s="3">
         <v>4927200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AH54" s="3">
         <v>5238600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AI54" s="3">
         <v>3484400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AJ54" s="3">
         <v>3507800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AK54" s="3">
         <v>3655600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AL54" s="3">
         <v>3703600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AM54" s="3">
         <v>3537000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AN54" s="3">
         <v>2365100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AO54" s="3">
         <v>2377100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5838,12 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,115 +5881,131 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>129200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>126900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>119600</v>
+      </c>
+      <c r="H57" s="3">
         <v>115500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>87500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>118700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>105900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>142400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>109700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>140200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>154100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>134400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>141100</v>
       </c>
       <c r="N57" s="3">
         <v>140200</v>
       </c>
       <c r="O57" s="3">
+        <v>154100</v>
+      </c>
+      <c r="P57" s="3">
+        <v>134400</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>141100</v>
+      </c>
+      <c r="R57" s="3">
+        <v>140200</v>
+      </c>
+      <c r="S57" s="3">
         <v>152900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>134500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>136000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>142600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>126300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>127400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>103600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>116300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>115400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AB57" s="3">
         <v>114400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AC57" s="3">
         <v>104400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AD57" s="3">
         <v>125000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AE57" s="3">
         <v>118300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AF57" s="3">
         <v>159100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AG57" s="3">
         <v>114600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AH57" s="3">
         <v>145500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AI57" s="3">
         <v>64900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AJ57" s="3">
         <v>80700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AK57" s="3">
         <v>74600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AL57" s="3">
         <v>89400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AM57" s="3">
         <v>63500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AN57" s="3">
         <v>64500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AO57" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5502,20 +6037,20 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>295000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5576,160 +6111,184 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>3300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>6500</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>6700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>7900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>6800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>12600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>17900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>13400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>6300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>8000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>8000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>9700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>7100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>7700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AF59" s="3">
         <v>6600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AG59" s="3">
         <v>5600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AH59" s="3">
         <v>34900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AI59" s="3">
         <v>23300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AJ59" s="3">
         <v>7100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AK59" s="3">
         <v>8500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AL59" s="3">
         <v>4900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AM59" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AN59" s="3">
         <v>5400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AO59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>129200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>126900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>120300</v>
+      </c>
+      <c r="H60" s="3">
         <v>116100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>88200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>119500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>109300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>145800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>110000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>142700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>154400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>134500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>436700</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5790,222 +6349,258 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1683600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>968100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>889600</v>
+      </c>
+      <c r="G61" s="3">
+        <v>2368200</v>
+      </c>
+      <c r="H61" s="3">
         <v>2365200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>2360900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>2534600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>2322000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>2307800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>2579200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>2572600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>2565900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>2538000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>2189700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>2432800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>2393800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="T61" s="3">
         <v>2487000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="U61" s="3">
         <v>2579800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="V61" s="3">
         <v>2578000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="W61" s="3">
         <v>2576200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="X61" s="3">
         <v>2516500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="Y61" s="3">
         <v>2204500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Z61" s="3">
         <v>2203000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="AA61" s="3">
         <v>2201400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AB61" s="3">
         <v>2176900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AC61" s="3">
         <v>2211800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AD61" s="3">
         <v>2327300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AE61" s="3">
         <v>2536100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AF61" s="3">
         <v>2922700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AG61" s="3">
         <v>3019800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AH61" s="3">
         <v>3274900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AI61" s="3">
         <v>2146900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AJ61" s="3">
         <v>2138300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AK61" s="3">
         <v>2277800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AL61" s="3">
         <v>2279200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AM61" s="3">
         <v>2091600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AN61" s="3">
         <v>1386500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AO61" s="3">
         <v>1392000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1582500</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1591200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H62" s="3">
         <v>13700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>14000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>15400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>16100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>16600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>18400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>18700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>20000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>19100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>20900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>1200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>3500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>2400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>300</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>14700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AE62" s="3">
         <v>16200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AF62" s="3">
         <v>2000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AG62" s="3">
         <v>200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AH62" s="3">
         <v>4300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AI62" s="3">
         <v>10000</v>
       </c>
-      <c r="AF62" s="3" t="s">
+      <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AK62" s="3">
         <v>300</v>
       </c>
-      <c r="AH62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3">
         <v>100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AO62" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6706,20 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6825,20 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6944,139 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1863100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2679700</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2607600</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2501600</v>
+      </c>
+      <c r="H66" s="3">
         <v>2495000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>2463100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>2669500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>2447400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>2470200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>2707600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>2734000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>2740400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>2691600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>2647400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>2593600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>2562800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>2647200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>2740600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>2745000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>2733900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>2682700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>2331600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>2337000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>2336400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>2311200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>2338300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>2487400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>2693600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>3107800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AG66" s="3">
         <v>3140200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AH66" s="3">
         <v>3459600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AI66" s="3">
         <v>2245100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AJ66" s="3">
         <v>2226100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AK66" s="3">
         <v>2361300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AL66" s="3">
         <v>2373500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AM66" s="3">
         <v>2159400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AN66" s="3">
         <v>1456400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AO66" s="3">
         <v>1448500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +7114,12 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +7225,20 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +7344,20 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +7463,20 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,8 +7582,20 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6934,80 +7629,92 @@
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3">
         <v>-1233700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>-1213400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>-1203700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>-1161000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>-1120900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>-1111300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>-1088400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>-995100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-1006400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>-978200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>-947800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>-922600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>-907000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>-945500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>-915100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AG72" s="3">
         <v>-823800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AH72" s="3">
         <v>-831400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AI72" s="3">
         <v>-731100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AJ72" s="3">
         <v>-688000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AK72" s="3">
         <v>-675800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AL72" s="3">
         <v>-699600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AM72" s="3">
         <v>-638700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AN72" s="3">
         <v>-608300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AO72" s="3">
         <v>-589400</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7820,20 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7939,20 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +8058,139 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>511500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>788100</v>
+      </c>
+      <c r="F76" s="3">
+        <v>881000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>999800</v>
+      </c>
+      <c r="H76" s="3">
         <v>1065900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>1106700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>1152800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>1278600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>1329700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>1250400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>1255700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>1304600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>1336000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>1359600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>1386300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>1406200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>1415500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>1457100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>1496700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>1506000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>1528600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>1621000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>1609400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>1636700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>1666400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>1690400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>1705800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>1666600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>1696500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AG76" s="3">
         <v>1787000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AH76" s="3">
         <v>1779000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AI76" s="3">
         <v>1239400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AJ76" s="3">
         <v>1281700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AK76" s="3">
         <v>1294400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AL76" s="3">
         <v>1330000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AM76" s="3">
         <v>1377500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AN76" s="3">
         <v>908700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AO76" s="3">
         <v>928600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +8296,263 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-792100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="H81" s="3">
         <v>-41200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="I81" s="3">
         <v>-45900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="J81" s="3">
         <v>-148700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="K81" s="3">
         <v>-58400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>76200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>-5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>-37200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>-19600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>-12200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>17000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>-13400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>16900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>-66700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>37900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>-3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>10800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>65000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>-64800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>34000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>-57700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>-400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AJ81" s="3">
         <v>35900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AK81" s="3">
         <v>6300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AL81" s="3">
         <v>-18300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AM81" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AN81" s="3">
         <v>19100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AO81" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +8590,131 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F83" s="3">
+        <v>29100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="H83" s="3">
         <v>31000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>29700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>29800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>27200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>25500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>24900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>23800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>23700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>24500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>50000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>51500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="T83" s="3">
         <v>56100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="U83" s="3">
         <v>59000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="V83" s="3">
         <v>61200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="W83" s="3">
         <v>58300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="X83" s="3">
         <v>54400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>63200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Z83" s="3">
         <v>62000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="AA83" s="3">
         <v>61900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="AB83" s="3">
         <v>64100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AC83" s="3">
         <v>63000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AD83" s="3">
         <v>62200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AE83" s="3">
         <v>73700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AF83" s="3">
         <v>74100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AG83" s="3">
         <v>77500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AH83" s="3">
         <v>32500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AI83" s="3">
         <v>42300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AJ83" s="3">
         <v>86300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AK83" s="3">
         <v>44000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AL83" s="3">
         <v>47500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AM83" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AN83" s="3">
         <v>40600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AO83" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8820,20 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8939,20 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +9058,20 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +9177,20 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +9296,139 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-52900</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="H89" s="3">
         <v>32400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>-28600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>25700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>-17100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>31900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>26600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>32600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>20900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>36300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>51900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>39900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>43800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>58600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>50300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>62800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>41300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>59400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>57900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Z89" s="3">
         <v>67500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="AA89" s="3">
         <v>54900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AB89" s="3">
         <v>73600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AC89" s="3">
         <v>37600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AD89" s="3">
         <v>67200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AE89" s="3">
         <v>40300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AF89" s="3">
         <v>89000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AG89" s="3">
         <v>18700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AH89" s="3">
         <v>24800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AI89" s="3">
         <v>26700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AJ89" s="3">
         <v>93500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AK89" s="3">
         <v>35300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AL89" s="3">
         <v>41600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AM89" s="3">
         <v>26100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AN89" s="3">
         <v>69800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AO89" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +9466,12 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8622,80 +9505,92 @@
       <c r="M91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-67100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-47900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="T91" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="U91" s="3">
         <v>-36200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="V91" s="3">
         <v>-35000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="W91" s="3">
         <v>-61400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="X91" s="3">
         <v>-16000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="Y91" s="3">
         <v>-15300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Z91" s="3">
         <v>-35400</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AD91" s="3">
         <v>36100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AE91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AF91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AG91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AH91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AI91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AJ91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AK91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AL91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AM91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AN91" s="3">
         <v>-12600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AO91" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9696,20 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9815,139 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>9700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-10500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>79900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>8000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-16900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-37900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-27000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-66100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-63800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-53800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>66300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="T94" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>-8800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="V94" s="3">
         <v>-7300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-35200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-514400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>113900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Z94" s="3">
         <v>-41100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="AA94" s="3">
         <v>-22800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AB94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AC94" s="3">
         <v>42100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AD94" s="3">
         <v>238100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AE94" s="3">
         <v>370900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AF94" s="3">
         <v>18500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AG94" s="3">
         <v>250300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AH94" s="3">
         <v>611800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AI94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AJ94" s="3">
         <v>133900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AK94" s="3">
         <v>11000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AL94" s="3">
         <v>-523900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AM94" s="3">
         <v>-643700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AN94" s="3">
         <v>-18600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AO94" s="3">
         <v>-11500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,58 +9985,62 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="I96" s="3">
         <v>700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="J96" s="3">
         <v>600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="L96" s="3">
         <v>500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="M96" s="3">
         <v>500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="N96" s="3">
         <v>12200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="O96" s="3">
         <v>12100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="P96" s="3">
         <v>12100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="Q96" s="3">
         <v>26700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="R96" s="3">
         <v>-26700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="S96" s="3">
         <v>-26700</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-26600</v>
       </c>
       <c r="T96" s="3">
         <v>-26600</v>
@@ -9117,16 +10052,16 @@
         <v>-26600</v>
       </c>
       <c r="W96" s="3">
-        <v>-26500</v>
+        <v>-26600</v>
       </c>
       <c r="X96" s="3">
-        <v>-26500</v>
+        <v>-26600</v>
       </c>
       <c r="Y96" s="3">
-        <v>-26500</v>
+        <v>-26600</v>
       </c>
       <c r="Z96" s="3">
-        <v>-26500</v>
+        <v>-26600</v>
       </c>
       <c r="AA96" s="3">
         <v>-26500</v>
@@ -9135,34 +10070,46 @@
         <v>-26500</v>
       </c>
       <c r="AC96" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-26400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AH96" s="3">
         <v>-42700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AI96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AJ96" s="3">
         <v>-85300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AK96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AL96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AM96" s="3">
         <v>-41400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AN96" s="3">
         <v>-61200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AO96" s="3">
         <v>-30600</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +10215,20 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +10334,20 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,115 +10453,139 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>75000</v>
+      </c>
+      <c r="F100" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="H100" s="3">
         <v>-6600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-185000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>133300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>10900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-24700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>19900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>32300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>23000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>10600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-122300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="T100" s="3">
         <v>-121600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="U100" s="3">
         <v>-26900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="V100" s="3">
         <v>-27000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="W100" s="3">
         <v>29900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="X100" s="3">
         <v>273500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="Y100" s="3">
         <v>-27200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>-27200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>-4500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="AB100" s="3">
         <v>-76300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AC100" s="3">
         <v>-146400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AD100" s="3">
         <v>-237600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AE100" s="3">
         <v>-402900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AF100" s="3">
         <v>-107500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AG100" s="3">
         <v>-283400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AH100" s="3">
         <v>-609600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AI100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AJ100" s="3">
         <v>-226000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AK100" s="3">
         <v>-43800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AL100" s="3">
         <v>-50600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AM100" s="3">
         <v>1157300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AN100" s="3">
         <v>-67000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AO100" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9624,17 +10619,17 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9696,111 +10691,135 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-32800</v>
+      </c>
+      <c r="H102" s="3">
         <v>15300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-198500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>238900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-9700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>17400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-12900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>13800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>11100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-12200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>-71300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>14500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>28500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>35900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>-181400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>144600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>-800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>27500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AB102" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AC102" s="3">
         <v>-66700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AD102" s="3">
         <v>67700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AE102" s="3">
         <v>8300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AG102" s="3">
         <v>-14300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AH102" s="3">
         <v>26900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AI102" s="3">
         <v>-9100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AJ102" s="3">
         <v>1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AK102" s="3">
         <v>2500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AL102" s="3">
         <v>-532600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AM102" s="3">
         <v>538800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AN102" s="3">
         <v>-17000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AO102" s="3">
         <v>-17000</v>
       </c>
     </row>
